--- a/ncxlxs/pack__ncxlsx__초6-1_사회_필수.xlsx
+++ b/ncxlxs/pack__ncxlsx__초6-1_사회_필수.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D1001"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>법</v>
+        <v>박정희</v>
       </c>
       <c r="B62" t="str">
-        <v>사람들이 사회생활을 유지하기 위해 국가가 강제로 지키도록 만든 규범.</v>
+        <v>대한민국의 제5~9대 대통령. 장기 집권 중 1979년 김재규 중앙정보부장의 총격으로 사망</v>
       </c>
       <c r="C62" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1269,38 +1269,38 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>법률안</v>
+        <v>법</v>
       </c>
       <c r="B63" t="str">
-        <v>입법부에서 새로운 규칙을 만들거나 고치기 위해 내놓은 문서.</v>
+        <v>사람들이 사회생활을 유지하기 위해 국가가 강제로 지키도록 만든 규범.</v>
       </c>
       <c r="C63" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>법원</v>
+        <v>법률안</v>
       </c>
       <c r="B64" t="str">
-        <v>사람들 사이에 다툼이 생기거나 범죄가 발생했을 때 규칙에 따라 재판을 하는 국가 기관.</v>
+        <v>입법부에서 새로운 규칙을 만들거나 고치기 위해 내놓은 문서.</v>
       </c>
       <c r="C64" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>변호사</v>
+        <v>법원</v>
       </c>
       <c r="B65" t="str">
-        <v>재판에서 억울한 사람을 대신해 권리를 지켜주는 법률 전문가.</v>
+        <v>사람들 사이에 다툼이 생기거나 범죄가 발생했을 때 규칙에 따라 재판을 하는 국가 기관.</v>
       </c>
       <c r="C65" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1311,206 +1311,206 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>보통 선거</v>
+        <v>변호사</v>
       </c>
       <c r="B66" t="str">
-        <v>일정한 나이가 되면 성별, 재산, 신분 등에 관계없이 누구나 참여할 수 있는 원칙.</v>
+        <v>재판에서 억울한 사람을 대신해 권리를 지켜주는 법률 전문가.</v>
       </c>
       <c r="C66" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>본초 자오선</v>
+        <v>보통 선거</v>
       </c>
       <c r="B67" t="str">
-        <v>영국의 그리니치 천문대를 지나는 세로선으로, 위치를 정하는 기준이 되는 세로 0도 선.</v>
+        <v>일정한 나이가 되면 성별, 재산, 신분 등에 관계없이 누구나 참여할 수 있는 원칙.</v>
       </c>
       <c r="C67" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>북반구</v>
+        <v>본초 자오선</v>
       </c>
       <c r="B68" t="str">
-        <v>가로 기준 0도인 선을 바탕으로 지구의 북쪽 절반 부분.</v>
+        <v>영국의 그리니치 천문대를 지나는 세로선으로, 위치를 정하는 기준이 되는 세로 0도 선.</v>
       </c>
       <c r="C68" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>북위</v>
+        <v>북반구</v>
       </c>
       <c r="B69" t="str">
-        <v>가로 기준 0도인 선을 바탕으로 북쪽으로 잰 위치를 나타내는 각도.</v>
+        <v>가로 기준 0도인 선을 바탕으로 지구의 북쪽 절반 부분.</v>
       </c>
       <c r="C69" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>북아메리카</v>
+        <v>북위</v>
       </c>
       <c r="B70" t="str">
-        <v>주로 적도 위쪽에 위치하며 미국, 캐나다 등이 있는 대륙.</v>
+        <v>가로 기준 0도인 선을 바탕으로 북쪽으로 잰 위치를 나타내는 각도.</v>
       </c>
       <c r="C70" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>북한 연구자</v>
+        <v>북아메리카</v>
       </c>
       <c r="B71" t="str">
-        <v>한반도의 북쪽 지역의 정치, 경제, 사회 등을 깊이 있게 공부하고 조사하는 사람.</v>
+        <v>주로 적도 위쪽에 위치하며 미국, 캐나다 등이 있는 대륙.</v>
       </c>
       <c r="C71" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>분단</v>
+        <v>북한 연구자</v>
       </c>
       <c r="B72" t="str">
-        <v>한 나라가 두 개 이상의 국가로 나뉘어 떨어지는 일.</v>
+        <v>한반도의 북쪽 지역의 정치, 경제, 사회 등을 깊이 있게 공부하고 조사하는 사람.</v>
       </c>
       <c r="C72" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>브라질</v>
+        <v>분단</v>
       </c>
       <c r="B73" t="str">
-        <v>남아메리카 대륙에서 가장 큰 나라로, 아마존 열대 우림이 있는 곳.</v>
+        <v>한 나라가 두 개 이상의 국가로 나뉘어 떨어지는 일.</v>
       </c>
       <c r="C73" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>비무장 지대</v>
+        <v>브라질</v>
       </c>
       <c r="B74" t="str">
-        <v>남북한이 서로 군대나 무기를 배치하지 않기로 약속한 군사 분계선 주변의 구역.</v>
+        <v>남아메리카 대륙에서 가장 큰 나라로, 아마존 열대 우림이 있는 곳.</v>
       </c>
       <c r="C74" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>비밀 선거</v>
+        <v>비무장 지대</v>
       </c>
       <c r="B75" t="str">
-        <v>누구에게 표를 던졌는지 다른 사람이 알 수 없도록 하는 원칙.</v>
+        <v>남북한이 서로 군대나 무기를 배치하지 않기로 약속한 군사 분계선 주변의 구역.</v>
       </c>
       <c r="C75" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>4·19 혁명</v>
+        <v>비밀 선거</v>
       </c>
       <c r="B76" t="str">
-        <v>1960년 부정 투표에 항의하여 학생과 시민들이 이승만 정권을 무너뜨린 민주화 운동.</v>
+        <v>누구에게 표를 던졌는지 다른 사람이 알 수 없도록 하는 원칙.</v>
       </c>
       <c r="C76" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>사회 관계망 서비스</v>
+        <v>4·19 혁명</v>
       </c>
       <c r="B77" t="str">
-        <v>인터넷상에서 사람들과 인맥을 맺고 정보를 주고받을 수 있는 온라인 플랫폼.</v>
+        <v>1960년 부정 투표에 항의하여 학생과 시민들이 이승만 정권을 무너뜨린 민주화 운동.</v>
       </c>
       <c r="C77" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>산마리노</v>
+        <v>사회 관계망 서비스</v>
       </c>
       <c r="B78" t="str">
-        <v>유럽의 이탈리아 반도 안에 있는 아주 작은 면적의 나라.</v>
+        <v>인터넷상에서 사람들과 인맥을 맺고 정보를 주고받을 수 있는 온라인 플랫폼.</v>
       </c>
       <c r="C78" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>산업화</v>
+        <v>산마리노</v>
       </c>
       <c r="B79" t="str">
-        <v>농업 중심의 사회에서 공업 중심으로 바뀌면서 기계를 이용해 물건을 대량으로 생산하게 된 변화.</v>
+        <v>유럽의 이탈리아 반도 안에 있는 아주 작은 면적의 나라.</v>
       </c>
       <c r="C79" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>삼심 제도</v>
+        <v>산업화</v>
       </c>
       <c r="B80" t="str">
-        <v>한 사건에 대해 세 번까지 재판을 받을 수 있도록 하여 억울한 사람이 없도록 하는 제도.</v>
+        <v>농업 중심의 사회에서 공업 중심으로 바뀌면서 기계를 이용해 물건을 대량으로 생산하게 된 변화.</v>
       </c>
       <c r="C80" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1521,66 +1521,66 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>서경</v>
+        <v>삼심 제도</v>
       </c>
       <c r="B81" t="str">
-        <v>영국의 0도 세로선을 기준으로 서쪽으로 잰 위치 각도.</v>
+        <v>한 사건에 대해 세 번까지 재판을 받을 수 있도록 하여 억울한 사람이 없도록 하는 제도.</v>
       </c>
       <c r="C81" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>선거</v>
+        <v>서경</v>
       </c>
       <c r="B82" t="str">
-        <v>국민이 자신들을 대신해서 국가나 지역의 일을 맡아볼 대표를 투표로 뽑는 일.</v>
+        <v>영국의 0도 세로선을 기준으로 서쪽으로 잰 위치 각도.</v>
       </c>
       <c r="C82" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>선거 공보</v>
+        <v>선거</v>
       </c>
       <c r="B83" t="str">
-        <v>후보자의 정보와 공약을 적어서 시민들의 집으로 보내주는 인쇄물.</v>
+        <v>국민이 자신들을 대신해서 국가나 지역의 일을 맡아볼 대표를 투표로 뽑는 일.</v>
       </c>
       <c r="C83" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>선거 공약</v>
+        <v>선거 공보</v>
       </c>
       <c r="B84" t="str">
-        <v>후보자가 자신이 당선되면 국민을 위해 어떤 일을 하겠다고 내세우는 굳은 약속.</v>
+        <v>후보자의 정보와 공약을 적어서 시민들의 집으로 보내주는 인쇄물.</v>
       </c>
       <c r="C84" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>선거 과정</v>
+        <v>선거 공약</v>
       </c>
       <c r="B85" t="str">
-        <v>대표를 뽑기 위해 후보를 등록하고 운동을 거쳐 표를 던지고 결과를 발표하는 모든 순서.</v>
+        <v>후보자가 자신이 당선되면 국민을 위해 어떤 일을 하겠다고 내세우는 굳은 약속.</v>
       </c>
       <c r="C85" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1591,24 +1591,24 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>선거 관리 위원회</v>
+        <v>선거 과정</v>
       </c>
       <c r="B86" t="str">
-        <v>대표를 선출하는 모든 과정이 공정하게 이루어지도록 관리하는 독립된 국가 기관.</v>
+        <v>대표를 뽑기 위해 후보를 등록하고 운동을 거쳐 표를 던지고 결과를 발표하는 모든 순서.</v>
       </c>
       <c r="C86" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>선거 관리 위원회 공무원</v>
+        <v>선거 관리 위원회</v>
       </c>
       <c r="B87" t="str">
-        <v>대표를 선출하는 과정이 공정하게 이루어지도록 해당 기관에서 일하는 사람.</v>
+        <v>대표를 선출하는 모든 과정이 공정하게 이루어지도록 관리하는 독립된 국가 기관.</v>
       </c>
       <c r="C87" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1619,178 +1619,178 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>선거 벽보</v>
+        <v>선거 관리 위원회 공무원</v>
       </c>
       <c r="B88" t="str">
-        <v>후보자의 사진과 약속을 적어 길거리나 벽에 붙여놓은 포스터.</v>
+        <v>대표를 선출하는 과정이 공정하게 이루어지도록 해당 기관에서 일하는 사람.</v>
       </c>
       <c r="C88" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>선거 연설문</v>
+        <v>선거 벽보</v>
       </c>
       <c r="B89" t="str">
-        <v>후보자가 대중 앞에서 자신의 생각과 약속을 발표하기 위해 쓴 글.</v>
+        <v>후보자의 사진과 약속을 적어 길거리나 벽에 붙여놓은 포스터.</v>
       </c>
       <c r="C89" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D89">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>선거 운동</v>
+        <v>선거 연설문</v>
       </c>
       <c r="B90" t="str">
-        <v>후보자가 사람들에게 자신을 알리고 지지해 달라고 호소하는 활동.</v>
+        <v>후보자가 대중 앞에서 자신의 생각과 약속을 발표하기 위해 쓴 글.</v>
       </c>
       <c r="C90" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>선거 원칙</v>
+        <v>선거 운동</v>
       </c>
       <c r="B91" t="str">
-        <v>대표를 뽑을 때 반드시 지켜야 하는 네 가지 기본 규칙.</v>
+        <v>후보자가 사람들에게 자신을 알리고 지지해 달라고 호소하는 활동.</v>
       </c>
       <c r="C91" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>선거인 명부 작성</v>
+        <v>선거 원칙</v>
       </c>
       <c r="B92" t="str">
-        <v>참여할 권리가 있는 사람들의 이름과 정보를 미리 조사하여 목록으로 만드는 일.</v>
+        <v>대표를 뽑을 때 반드시 지켜야 하는 네 가지 기본 규칙.</v>
       </c>
       <c r="C92" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>선거 토론회</v>
+        <v>선거인 명부 작성</v>
       </c>
       <c r="B93" t="str">
-        <v>후보자들이 모여서 서로의 정책이나 생각에 대해 질문하고 대답하며 의논하는 자리.</v>
+        <v>참여할 권리가 있는 사람들의 이름과 정보를 미리 조사하여 목록으로 만드는 일.</v>
       </c>
       <c r="C93" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>선상 투표</v>
+        <v>선거 토론회</v>
       </c>
       <c r="B94" t="str">
-        <v>배를 타고 먼 바다에 나가 있는 선원들이 배 위에서 표를 던지는 방식.</v>
+        <v>후보자들이 모여서 서로의 정책이나 생각에 대해 질문하고 대답하며 의논하는 자리.</v>
       </c>
       <c r="C94" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>세계지도</v>
+        <v>선상 투표</v>
       </c>
       <c r="B95" t="str">
-        <v>둥근 지구 전체의 모습을 평면인 종이 위에 그려 놓은 그림.</v>
+        <v>배를 타고 먼 바다에 나가 있는 선원들이 배 위에서 표를 던지는 방식.</v>
       </c>
       <c r="C95" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>시민군</v>
+        <v>세계지도</v>
       </c>
       <c r="B96" t="str">
-        <v>1980년 광주에서 신군부에 맞서 스스로 무장을 하고 일어난 평범한 사람들.</v>
+        <v>둥근 지구 전체의 모습을 평면인 종이 위에 그려 놓은 그림.</v>
       </c>
       <c r="C96" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>시차</v>
+        <v>시민군</v>
       </c>
       <c r="B97" t="str">
-        <v>지구가 돌면서 생기는, 세계 여러 지역 간의 시간 차이.</v>
+        <v>1980년 광주에서 신군부에 맞서 스스로 무장을 하고 일어난 평범한 사람들.</v>
       </c>
       <c r="C97" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>신문</v>
+        <v>시차</v>
       </c>
       <c r="B98" t="str">
-        <v>사회에서 일어나는 여러 가지 사건이나 소식을 글과 사진으로 전하는 종이 매체.</v>
+        <v>지구가 돌면서 생기는, 세계 여러 지역 간의 시간 차이.</v>
       </c>
       <c r="C98" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>실향민</v>
+        <v>신문</v>
       </c>
       <c r="B99" t="str">
-        <v>전쟁이나 분단 등의 이유로 고향을 떠난 후 다시 돌아가지 못하는 사람.</v>
+        <v>사회에서 일어나는 여러 가지 사건이나 소식을 글과 사진으로 전하는 종이 매체.</v>
       </c>
       <c r="C99" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>심의</v>
+        <v>실향민</v>
       </c>
       <c r="B100" t="str">
-        <v>어떤 안건을 결정하기 전에 깊이 생각하고 의논하는 일.</v>
+        <v>전쟁이나 분단 등의 이유로 고향을 떠난 후 다시 돌아가지 못하는 사람.</v>
       </c>
       <c r="C100" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1801,178 +1801,178 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>아르헨티나</v>
+        <v>심의</v>
       </c>
       <c r="B101" t="str">
-        <v>남아메리카 남부에 있는 나라로, 탱고 춤과 축구로 유명함.</v>
+        <v>어떤 안건을 결정하기 전에 깊이 생각하고 의논하는 일.</v>
       </c>
       <c r="C101" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>아바이 마을</v>
+        <v>아르헨티나</v>
       </c>
       <c r="B102" t="str">
-        <v>한국 전쟁 때 북쪽에서 내려온 피난민들이 모여 살게 된 강원도 속초의 동네.</v>
+        <v>남아메리카 남부에 있는 나라로, 탱고 춤과 축구로 유명함.</v>
       </c>
       <c r="C102" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>아시아</v>
+        <v>아바이 마을</v>
       </c>
       <c r="B103" t="str">
-        <v>우리나라가 속해 있으며 세계에서 가장 크고 인구가 많은 대륙.</v>
+        <v>한국 전쟁 때 북쪽에서 내려온 피난민들이 모여 살게 된 강원도 속초의 동네.</v>
       </c>
       <c r="C103" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>아프리카</v>
+        <v>아시아</v>
       </c>
       <c r="B104" t="str">
-        <v>사하라 사막과 넓은 초원이 펼쳐진, 세계에서 두 번째로 큰 대륙.</v>
+        <v>우리나라가 속해 있으며 세계에서 가장 크고 인구가 많은 대륙.</v>
       </c>
       <c r="C104" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>에티오피아</v>
+        <v>아프리카</v>
       </c>
       <c r="B105" t="str">
-        <v>아프리카 동부에 있는 나라로 커피가 처음 발견된 곳으로 알려짐.</v>
+        <v>사하라 사막과 넓은 초원이 펼쳐진, 세계에서 두 번째로 큰 대륙.</v>
       </c>
       <c r="C105" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>여론</v>
+        <v>에티오피아</v>
       </c>
       <c r="B106" t="str">
-        <v>사회의 어떤 문제에 대하여 많은 사람들이 공통적으로 가지는 의견.</v>
+        <v>아프리카 동부에 있는 나라로 커피가 처음 발견된 곳으로 알려짐.</v>
       </c>
       <c r="C106" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D106">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>예산안</v>
+        <v>여론</v>
       </c>
       <c r="B107" t="str">
-        <v>정부가 1년 동안 나라의 돈을 어디에 어떻게 쓸 것인지 계획하여 입법부에 제출하는 문서.</v>
+        <v>사회의 어떤 문제에 대하여 많은 사람들이 공통적으로 가지는 의견.</v>
       </c>
       <c r="C107" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>오세아니아</v>
+        <v>예산안</v>
       </c>
       <c r="B108" t="str">
-        <v>태평양 남서부에 있는 대륙으로 오스트레일리아와 뉴질랜드 등이 포함됨.</v>
+        <v>정부가 1년 동안 나라의 돈을 어디에 어떻게 쓸 것인지 계획하여 입법부에 제출하는 문서.</v>
       </c>
       <c r="C108" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D108">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>오산 죽미령 평화 공원</v>
+        <v>오세아니아</v>
       </c>
       <c r="B109" t="str">
-        <v>6·25 전쟁 당시 유엔군이 북한군과 처음으로 치열하게 싸웠던 곳을 기리는 장소.</v>
+        <v>태평양 남서부에 있는 대륙으로 오스트레일리아와 뉴질랜드 등이 포함됨.</v>
       </c>
       <c r="C109" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>오스트레일리아</v>
+        <v>오산 죽미령 평화 공원</v>
       </c>
       <c r="B110" t="str">
-        <v>캥거루와 코알라가 살고 있으며 대륙 전체가 하나의 나라인 곳.</v>
+        <v>6·25 전쟁 당시 유엔군이 북한군과 처음으로 치열하게 싸웠던 곳을 기리는 장소.</v>
       </c>
       <c r="C110" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>5.18 민주화 운동</v>
+        <v>오스트레일리아</v>
       </c>
       <c r="B111" t="str">
-        <v>1980년 광주에서 부당한 권력에 맞서 시민들이 요구하며 벌인 항쟁.</v>
+        <v>캥거루와 코알라가 살고 있으며 대륙 전체가 하나의 나라인 곳.</v>
       </c>
       <c r="C111" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>외교관</v>
+        <v>5.18 민주화 운동</v>
       </c>
       <c r="B112" t="str">
-        <v>외국에 머물면서 우리나라를 대표하여 다른 나라와 관계를 맺고 협상하는 공무원.</v>
+        <v>1980년 광주에서 부당한 권력에 맞서 시민들이 요구하며 벌인 항쟁.</v>
       </c>
       <c r="C112" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>위도</v>
+        <v>외교관</v>
       </c>
       <c r="B113" t="str">
-        <v>지구의 가로 위치를 나타내는 선으로, 적도를 0도로 하여 남북으로 잰 각도.</v>
+        <v>외국에 머물면서 우리나라를 대표하여 다른 나라와 관계를 맺고 협상하는 공무원.</v>
       </c>
       <c r="C113" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -1983,164 +1983,164 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>위르겐 힌츠페터</v>
+        <v>위도</v>
       </c>
       <c r="B114" t="str">
-        <v>1980년 광주의 참상을 카메라에 담아 전 세계에 알린 독일의 기자.</v>
+        <v>지구의 가로 위치를 나타내는 선으로, 적도를 0도로 하여 남북으로 잰 각도.</v>
       </c>
       <c r="C114" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>유권자</v>
+        <v>위르겐 힌츠페터</v>
       </c>
       <c r="B115" t="str">
-        <v>일정한 나이가 되어 대표를 뽑는 과정에 참여할 권리를 가진 사람.</v>
+        <v>1980년 광주의 참상을 카메라에 담아 전 세계에 알린 독일의 기자.</v>
       </c>
       <c r="C115" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>유럽</v>
+        <v>유권자</v>
       </c>
       <c r="B116" t="str">
-        <v>아시아의 서쪽에 붙어 있는 대륙으로 영국, 프랑스, 독일 등이 속함.</v>
+        <v>일정한 나이가 되어 대표를 뽑는 과정에 참여할 권리를 가진 사람.</v>
       </c>
       <c r="C116" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>6월 민주 항쟁</v>
+        <v>유럽</v>
       </c>
       <c r="B117" t="str">
-        <v>1987년, 시민들이 직접 최고 책임자를 뽑게 해달라고 요구하며 전국적으로 일어난 시위.</v>
+        <v>아시아의 서쪽에 붙어 있는 대륙으로 영국, 프랑스, 독일 등이 속함.</v>
       </c>
       <c r="C117" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>이산가족</v>
+        <v>6월 민주 항쟁</v>
       </c>
       <c r="B118" t="str">
-        <v>6·25 전쟁 등으로 인해 남과 북으로 흩어져서 서로 만나지 못하고 있는 혈육.</v>
+        <v>1987년, 시민들이 직접 최고 책임자를 뽑게 해달라고 요구하며 전국적으로 일어난 시위.</v>
       </c>
       <c r="C118" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>이승만</v>
+        <v>이산가족</v>
       </c>
       <c r="B119" t="str">
-        <v>우리나라의 1, 2, 3대 최고 책임자로 장기 집권을 하려다 4.19 혁명으로 물러난 인물.</v>
+        <v>6·25 전쟁 등으로 인해 남과 북으로 흩어져서 서로 만나지 못하고 있는 혈육.</v>
       </c>
       <c r="C119" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D119">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>이집트</v>
+        <v>이승만</v>
       </c>
       <c r="B120" t="str">
-        <v>아프리카 북동부에 있는 나라로 피라미드와 스핑크스로 유명함.</v>
+        <v>우리나라의 1, 2, 3대 최고 책임자로 장기 집권을 하려다 4.19 혁명으로 물러난 인물.</v>
       </c>
       <c r="C120" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>이한열</v>
+        <v>이집트</v>
       </c>
       <c r="B121" t="str">
-        <v>1987년 시위 도중 최루탄에 맞아 쓰러져 6월 항쟁의 기폭제가 된 대학생.</v>
+        <v>아프리카 북동부에 있는 나라로 피라미드와 스핑크스로 유명함.</v>
       </c>
       <c r="C121" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>인도양</v>
+        <v>이한열</v>
       </c>
       <c r="B122" t="str">
-        <v>아프리카, 아시아, 오세아니아, 남극 대륙 사이에 있는 바다.</v>
+        <v>1987년 시위 도중 최루탄에 맞아 쓰러져 6월 항쟁의 기폭제가 된 대학생.</v>
       </c>
       <c r="C122" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>인사 청문회</v>
+        <v>인도양</v>
       </c>
       <c r="B123" t="str">
-        <v>고위 공직자로 지명된 사람이 그 자리에 적합한 능력을 갖추었는지 입법부에서 묻고 검증하는 과정.</v>
+        <v>아프리카, 아시아, 오세아니아, 남극 대륙 사이에 있는 바다.</v>
       </c>
       <c r="C123" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>일본</v>
+        <v>인사 청문회</v>
       </c>
       <c r="B124" t="str">
-        <v>아시아 동쪽에 위치하며 네 개의 큰 섬으로 이루어진 이웃 나라.</v>
+        <v>고위 공직자로 지명된 사람이 그 자리에 적합한 능력을 갖추었는지 입법부에서 묻고 검증하는 과정.</v>
       </c>
       <c r="C124" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>자동차</v>
+        <v>일본</v>
       </c>
       <c r="B125" t="str">
-        <v>바퀴가 네 개 달려 있고 엔진의 힘으로 도로를 달리는 교통수단.</v>
+        <v>아시아 동쪽에 위치하며 네 개의 큰 섬으로 이루어진 이웃 나라.</v>
       </c>
       <c r="C125" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2151,94 +2151,94 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>장사 상륙 작전 전승 기념관</v>
+        <v>자동차</v>
       </c>
       <c r="B126" t="str">
-        <v>6·25 전쟁 당시 학도병들이 희생하며 인천을 향한 적의 시선을 돌린 전투를 기리는 영덕의 장소.</v>
+        <v>바퀴가 네 개 달려 있고 엔진의 힘으로 도로를 달리는 교통수단.</v>
       </c>
       <c r="C126" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D126">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>재판</v>
+        <v>장사 상륙 작전 전승 기념관</v>
       </c>
       <c r="B127" t="str">
-        <v>사람들 사이에 다툼이 생겼을 때 법원에서 옳고 그름을 가리는 일.</v>
+        <v>6·25 전쟁 당시 학도병들이 희생하며 인천을 향한 적의 시선을 돌린 전투를 기리는 영덕의 장소.</v>
       </c>
       <c r="C127" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>저위도</v>
+        <v>재판</v>
       </c>
       <c r="B128" t="str">
-        <v>가로 기준 0도인 선 주변의 지역으로, 일 년 내내 날씨가 덥고 따뜻한 곳.</v>
+        <v>사람들 사이에 다툼이 생겼을 때 법원에서 옳고 그름을 가리는 일.</v>
       </c>
       <c r="C128" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>적도</v>
+        <v>저위도</v>
       </c>
       <c r="B129" t="str">
-        <v>지구를 남과 북으로 똑같이 나누는 가상의 가로선으로, 가로 기준 0도가 되는 곳.</v>
+        <v>가로 기준 0도인 선 주변의 지역으로, 일 년 내내 날씨가 덥고 따뜻한 곳.</v>
       </c>
       <c r="C129" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>전두환</v>
+        <v>적도</v>
       </c>
       <c r="B130" t="str">
-        <v>12.12 군사 반란으로 권력을 잡고 1980년 광주 시민들을 무력으로 진압한 11, 12대 최고 책임자.</v>
+        <v>지구를 남과 북으로 똑같이 나누는 가상의 가로선으로, 가로 기준 0도가 되는 곳.</v>
       </c>
       <c r="C130" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D130">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>전태일</v>
+        <v>전두환</v>
       </c>
       <c r="B131" t="str">
-        <v>노동자들의 열악한 환경을 알리기 위해 근로 기준법 준수를 외치며 희생한 인물.</v>
+        <v>12.12 군사 반란으로 권력을 잡고 1980년 광주 시민들을 무력으로 진압한 11, 12대 최고 책임자.</v>
       </c>
       <c r="C131" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>주민 소환제</v>
+        <v>전태일</v>
       </c>
       <c r="B132" t="str">
-        <v>지역의 대표나 공직자가 일을 잘못했을 때, 지역 사람들이 뜻을 모아 그 사람을 자리에서 물러나게 할 수 있는 제도.</v>
+        <v>노동자들의 열악한 환경을 알리기 위해 근로 기준법 준수를 외치며 희생한 인물.</v>
       </c>
       <c r="C132" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2249,150 +2249,150 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>중국</v>
+        <v>주민 소환제</v>
       </c>
       <c r="B133" t="str">
-        <v>아시아 동부에 있는 나라로 세계에서 인구가 매우 많고 면적이 넓은 이웃 국가.</v>
+        <v>지역의 대표나 공직자가 일을 잘못했을 때, 지역 사람들이 뜻을 모아 그 사람을 자리에서 물러나게 할 수 있는 제도.</v>
       </c>
       <c r="C133" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>중위도</v>
+        <v>중국</v>
       </c>
       <c r="B134" t="str">
-        <v>0도 가로선과 극지방의 중간 지역으로, 사계절의 변화가 뚜렷하게 나타나는 곳.</v>
+        <v>아시아 동부에 있는 나라로 세계에서 인구가 매우 많고 면적이 넓은 이웃 국가.</v>
       </c>
       <c r="C134" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>중화학 공업</v>
+        <v>중위도</v>
       </c>
       <c r="B135" t="str">
-        <v>철강, 배, 자동차 등 무겁고 부피가 큰 물건을 만들거나 화학 제품을 만드는 산업.</v>
+        <v>0도 가로선과 극지방의 중간 지역으로, 사계절의 변화가 뚜렷하게 나타나는 곳.</v>
       </c>
       <c r="C135" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>지구본</v>
+        <v>중화학 공업</v>
       </c>
       <c r="B136" t="str">
-        <v>둥근 지구의 생김새를 본떠서 작게 만든 모형.</v>
+        <v>철강, 배, 자동차 등 무겁고 부피가 큰 물건을 만들거나 화학 제품을 만드는 산업.</v>
       </c>
       <c r="C136" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>지방 자치제</v>
+        <v>지구본</v>
       </c>
       <c r="B137" t="str">
-        <v>지역의 일과 문제를 그 지역에 사는 사람들이 스스로 결정하고 처리하는 제도.</v>
+        <v>둥근 지구의 생김새를 본떠서 작게 만든 모형.</v>
       </c>
       <c r="C137" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>직선제</v>
+        <v>지방 자치제</v>
       </c>
       <c r="B138" t="str">
-        <v>다른 사람을 거치지 않고, 시민들이 자신의 손으로 직접 대표나 통치자를 뽑는 방식.</v>
+        <v>지역의 일과 문제를 그 지역에 사는 사람들이 스스로 결정하고 처리하는 제도.</v>
       </c>
       <c r="C138" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>지원</v>
+        <v>직선제</v>
       </c>
       <c r="B139" t="str">
-        <v>어떤 일이나 사람을 돕기 위해 돈이나 물건, 힘을 보태어 주는 것.</v>
+        <v>다른 사람을 거치지 않고, 시민들이 자신의 손으로 직접 대표나 통치자를 뽑는 방식.</v>
       </c>
       <c r="C139" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>7.4 남북 공동 성명</v>
+        <v>지원</v>
       </c>
       <c r="B140" t="str">
-        <v>1972년 남과 북이 자주, 평화, 민족 대단결이라는 통일의 3대 원칙을 처음으로 함께 발표한 일.</v>
+        <v>어떤 일이나 사람을 돕기 위해 돈이나 물건, 힘을 보태어 주는 것.</v>
       </c>
       <c r="C140" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>칠레</v>
+        <v>7.4 남북 공동 성명</v>
       </c>
       <c r="B141" t="str">
-        <v>남아메리카 대륙의 서쪽 해안을 따라 남북으로 아주 길게 뻗어 있는 나라.</v>
+        <v>1972년 남과 북이 자주, 평화, 민족 대단결이라는 통일의 3대 원칙을 처음으로 함께 발표한 일.</v>
       </c>
       <c r="C141" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D141">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>캐나다</v>
+        <v>칠레</v>
       </c>
       <c r="B142" t="str">
-        <v>북아메리카 대륙 북부에 있는 나라로 세계에서 두 번째로 땅이 넓음.</v>
+        <v>남아메리카 대륙의 서쪽 해안을 따라 남북으로 아주 길게 뻗어 있는 나라.</v>
       </c>
       <c r="C142" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>태평양</v>
+        <v>캐나다</v>
       </c>
       <c r="B143" t="str">
-        <v>아시아, 오세아니아, 아메리카 대륙 사이에 있는 세계에서 가장 크고 깊은 바다.</v>
+        <v>북아메리카 대륙 북부에 있는 나라로 세계에서 두 번째로 땅이 넓음.</v>
       </c>
       <c r="C143" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2403,10 +2403,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>투표</v>
+        <v>태평양</v>
       </c>
       <c r="B144" t="str">
-        <v>어떤 일을 결정하거나 대표를 뽑을 때, 자신의 의견을 종이에 적거나 기계로 표시하여 내는 일.</v>
+        <v>아시아, 오세아니아, 아메리카 대륙 사이에 있는 세계에서 가장 크고 깊은 바다.</v>
       </c>
       <c r="C144" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2417,38 +2417,38 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>파나마 지협</v>
+        <v>투표</v>
       </c>
       <c r="B145" t="str">
-        <v>북아메리카와 남아메리카를 연결하는 좁은 땅으로, 운하가 있어 배가 지나다니는 곳.</v>
+        <v>어떤 일을 결정하거나 대표를 뽑을 때, 자신의 의견을 종이에 적거나 기계로 표시하여 내는 일.</v>
       </c>
       <c r="C145" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>평등 선거</v>
+        <v>파나마 지협</v>
       </c>
       <c r="B146" t="str">
-        <v>재산이나 학력에 상관없이 모든 사람이 누구나 똑같이 한 표씩만 행사할 수 있는 원칙.</v>
+        <v>북아메리카와 남아메리카를 연결하는 좁은 땅으로, 운하가 있어 배가 지나다니는 곳.</v>
       </c>
       <c r="C146" t="str">
         <v>삼봉초 6학년 사회</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>포항 종합 제철소</v>
+        <v>평등 선거</v>
       </c>
       <c r="B147" t="str">
-        <v>철광석을 녹여 쇳물을 만들고 철강 제품을 대량으로 생산하기 위해 바닷가에 세운 큰 공장.</v>
+        <v>재산이나 학력에 상관없이 모든 사람이 누구나 똑같이 한 표씩만 행사할 수 있는 원칙.</v>
       </c>
       <c r="C147" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>행정부</v>
+        <v>포항 종합 제철소</v>
       </c>
       <c r="B148" t="str">
-        <v>입법부에서 만든 법률을 바탕으로 나라의 살림을 실제로 맡아서 하는 국가 기관.</v>
+        <v>철광석을 녹여 쇳물을 만들고 철강 제품을 대량으로 생산하기 위해 바닷가에 세운 큰 공장.</v>
       </c>
       <c r="C148" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>허위 조작 정보</v>
+        <v>행정부</v>
       </c>
       <c r="B149" t="str">
-        <v>사실이 아닌 내용을 고의로 지어내어 퍼뜨리는 가짜 소식.</v>
+        <v>입법부에서 만든 법률을 바탕으로 나라의 살림을 실제로 맡아서 하는 국가 기관.</v>
       </c>
       <c r="C149" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>후보자 등록</v>
+        <v>허위 조작 정보</v>
       </c>
       <c r="B150" t="str">
-        <v>대표로 선출되기 위해 출마하려는 사람이 정해진 기간에 관련 서류를 제출하여 정식으로 인정받는 일.</v>
+        <v>사실이 아닌 내용을 고의로 지어내어 퍼뜨리는 가짜 소식.</v>
       </c>
       <c r="C150" t="str">
         <v>삼봉초 6학년 사회</v>
@@ -2501,21 +2501,35 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
+        <v>후보자 등록</v>
+      </c>
+      <c r="B151" t="str">
+        <v>대표로 선출되기 위해 출마하려는 사람이 정해진 기간에 관련 서류를 제출하여 정식으로 인정받는 일.</v>
+      </c>
+      <c r="C151" t="str">
+        <v>삼봉초 6학년 사회</v>
+      </c>
+      <c r="D151">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
         <v>휴전선</v>
       </c>
-      <c r="B151" t="str">
+      <c r="B152" t="str">
         <v>1953년 6·25 전쟁을 멈추기로 약속하면서 남한과 북한 사이에 그어진 경계선.</v>
       </c>
-      <c r="C151" t="str">
-        <v>삼봉초 6학년 사회</v>
-      </c>
-      <c r="D151">
+      <c r="C152" t="str">
+        <v>삼봉초 6학년 사회</v>
+      </c>
+      <c r="D152">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1001"/>
   </ignoredErrors>
 </worksheet>
 </file>